--- a/SRC_BAPIv2.2_VAL_TBL_EXPORT_E/Data/Arg-SRC_BAPIv2.2_VAL_TBL_EXPORT_E(EN).xlsx
+++ b/SRC_BAPIv2.2_VAL_TBL_EXPORT_E/Data/Arg-SRC_BAPIv2.2_VAL_TBL_EXPORT_E(EN).xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18943E07-53BF-4BCC-9A77-5035FF9A5CAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A747EEA4-08DA-4964-9929-49DBA3F955FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2985" windowWidth="15915" windowHeight="11385" xr2:uid="{1D813E3E-3342-4978-A98A-84363F7AA1D1}"/>
+    <workbookView xWindow="3015" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{1D813E3E-3342-4978-A98A-84363F7AA1D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -78,15 +78,40 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>xxx.xxx.xxx.xxx</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>xxx</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>xx</t>
+    <t>10.10.10.6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>310</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>D:\RPA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>工作區</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>\UiPath Foundation pack for Accelerators for SAP ECC\Output</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -94,18 +119,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -122,6 +147,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +192,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -176,9 +208,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -216,7 +248,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -322,7 +354,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -464,7 +496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -474,11 +506,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975296A4-EDFA-4C78-9FA0-6562751B9254}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -493,15 +525,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -512,7 +547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -520,7 +555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -528,7 +563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -536,7 +571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
